--- a/12604120.xlsx
+++ b/12604120.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD112F5-2A11-4798-B8B7-04636D578E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1837E289-DFC6-45B5-A980-E4C2FCAA332D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -268,6 +268,9 @@
   </si>
   <si>
     <t>yesterday I was travelling, so I couldn’t write anything.</t>
+  </si>
+  <si>
+    <t>preparing for ca</t>
   </si>
 </sst>
 </file>
@@ -1783,26 +1786,50 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B22" s="14">
+        <v>420</v>
+      </c>
+      <c r="C22" s="14">
+        <v>0</v>
+      </c>
+      <c r="D22" s="14">
+        <v>420</v>
+      </c>
+      <c r="E22" s="14">
+        <v>0</v>
+      </c>
+      <c r="F22" s="14">
+        <v>0</v>
+      </c>
+      <c r="G22" s="14">
+        <v>0</v>
+      </c>
+      <c r="H22" s="14">
+        <v>300</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>300</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>

--- a/12604120.xlsx
+++ b/12604120.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1837E289-DFC6-45B5-A980-E4C2FCAA332D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA3BA07B-DD76-4AAC-986E-7F4E3E32E2CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -271,6 +271,9 @@
   </si>
   <si>
     <t>preparing for ca</t>
+  </si>
+  <si>
+    <t>get prepared for ca</t>
   </si>
 </sst>
 </file>
@@ -1832,26 +1835,50 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B23" s="14">
+        <v>350</v>
+      </c>
+      <c r="C23" s="14">
+        <v>0</v>
+      </c>
+      <c r="D23" s="14">
+        <v>120</v>
+      </c>
+      <c r="E23" s="14">
+        <v>0</v>
+      </c>
+      <c r="F23" s="14">
+        <v>350</v>
+      </c>
+      <c r="G23" s="14">
+        <v>7</v>
+      </c>
+      <c r="H23" s="14">
+        <v>330</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>290</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>

--- a/12604120.xlsx
+++ b/12604120.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA3BA07B-DD76-4AAC-986E-7F4E3E32E2CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A36F269C-EDF3-4A78-92FC-0FF601238BFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -274,6 +274,9 @@
   </si>
   <si>
     <t>get prepared for ca</t>
+  </si>
+  <si>
+    <t>nothing do much</t>
   </si>
 </sst>
 </file>
@@ -1881,26 +1884,50 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B24" s="14">
+        <v>420</v>
+      </c>
+      <c r="C24" s="14">
+        <v>0</v>
+      </c>
+      <c r="D24" s="14">
+        <v>60</v>
+      </c>
+      <c r="E24" s="14">
+        <v>0</v>
+      </c>
+      <c r="F24" s="14">
+        <v>350</v>
+      </c>
+      <c r="G24" s="14">
+        <v>7</v>
+      </c>
+      <c r="H24" s="14">
+        <v>300</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>

--- a/12604120.xlsx
+++ b/12604120.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A36F269C-EDF3-4A78-92FC-0FF601238BFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{791DD16A-B690-4040-B495-7E257B026EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -277,6 +277,9 @@
   </si>
   <si>
     <t>nothing do much</t>
+  </si>
+  <si>
+    <t xml:space="preserve">today I learn some classes </t>
   </si>
 </sst>
 </file>
@@ -1930,26 +1933,48 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
+      <c r="A25" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B25" s="14">
+        <v>420</v>
+      </c>
       <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="D25" s="14">
+        <v>60</v>
+      </c>
+      <c r="E25" s="14">
+        <v>0</v>
+      </c>
+      <c r="F25" s="14">
+        <v>350</v>
+      </c>
+      <c r="G25" s="14">
+        <v>7</v>
+      </c>
+      <c r="H25" s="14">
+        <v>300</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>

--- a/12604120.xlsx
+++ b/12604120.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{791DD16A-B690-4040-B495-7E257B026EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{864D8410-6D7E-4926-B64D-FD0424AA08CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -280,6 +280,9 @@
   </si>
   <si>
     <t xml:space="preserve">today I learn some classes </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> I enjoyed the fresher party and solved some analytics problems.</t>
   </si>
 </sst>
 </file>
@@ -1976,27 +1979,51 @@
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+    <row r="26" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B26" s="14">
+        <v>420</v>
+      </c>
+      <c r="C26" s="14">
+        <v>30</v>
+      </c>
+      <c r="D26" s="14">
+        <v>90</v>
+      </c>
+      <c r="E26" s="14">
+        <v>30</v>
+      </c>
+      <c r="F26" s="14">
+        <v>150</v>
+      </c>
+      <c r="G26" s="14">
+        <v>3</v>
+      </c>
+      <c r="H26" s="14">
+        <v>300</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="13"/>

--- a/12604120.xlsx
+++ b/12604120.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{864D8410-6D7E-4926-B64D-FD0424AA08CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C37F36-E084-4619-B482-504950020214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -283,6 +283,9 @@
   </si>
   <si>
     <t xml:space="preserve"> I enjoyed the fresher party and solved some analytics problems.</t>
+  </si>
+  <si>
+    <t>solved some analytics problems.</t>
   </si>
 </sst>
 </file>
@@ -2026,26 +2029,50 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B27" s="14">
+        <v>360</v>
+      </c>
+      <c r="C27" s="14">
+        <v>0</v>
+      </c>
+      <c r="D27" s="14">
+        <v>120</v>
+      </c>
+      <c r="E27" s="14">
+        <v>0</v>
+      </c>
+      <c r="F27" s="14">
+        <v>150</v>
+      </c>
+      <c r="G27" s="14">
+        <v>3</v>
+      </c>
+      <c r="H27" s="14">
+        <v>300</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>

--- a/12604120.xlsx
+++ b/12604120.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C37F36-E084-4619-B482-504950020214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAAB51B5-FAE2-4296-8F41-091E0AE952C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -286,6 +286,9 @@
   </si>
   <si>
     <t>solved some analytics problems.</t>
+  </si>
+  <si>
+    <t>I will work on my project</t>
   </si>
 </sst>
 </file>
@@ -2075,26 +2078,50 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B28" s="14">
+        <v>360</v>
+      </c>
+      <c r="C28" s="14">
+        <v>30</v>
+      </c>
+      <c r="D28" s="14">
+        <v>120</v>
+      </c>
+      <c r="E28" s="14">
+        <v>65</v>
+      </c>
+      <c r="F28" s="14">
+        <v>0</v>
+      </c>
+      <c r="G28" s="14">
+        <v>0</v>
+      </c>
+      <c r="H28" s="14">
+        <v>420</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>995</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>445</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="13"/>

--- a/12604120.xlsx
+++ b/12604120.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAAB51B5-FAE2-4296-8F41-091E0AE952C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34125A5D-F943-4826-9EA1-1A1578C8C322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -289,6 +289,9 @@
   </si>
   <si>
     <t>I will work on my project</t>
+  </si>
+  <si>
+    <t>Stressed</t>
   </si>
 </sst>
 </file>
@@ -2124,26 +2127,48 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
+      <c r="A29" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B29" s="14">
+        <v>360</v>
+      </c>
       <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="D29" s="14">
+        <v>150</v>
+      </c>
+      <c r="E29" s="14">
+        <v>0</v>
+      </c>
+      <c r="F29" s="14">
+        <v>0</v>
+      </c>
+      <c r="G29" s="14">
+        <v>0</v>
+      </c>
+      <c r="H29" s="14">
+        <v>420</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>

--- a/12604120.xlsx
+++ b/12604120.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34125A5D-F943-4826-9EA1-1A1578C8C322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3FFE489-3858-46D0-9903-588DD7C04994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2171,26 +2171,48 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
+      <c r="A30" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B30" s="14">
+        <v>360</v>
+      </c>
       <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="D30" s="14">
+        <v>50</v>
+      </c>
+      <c r="E30" s="14">
+        <v>30</v>
+      </c>
+      <c r="F30" s="14">
+        <v>350</v>
+      </c>
+      <c r="G30" s="14">
+        <v>7</v>
+      </c>
+      <c r="H30" s="14">
+        <v>300</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>350</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="13"/>

--- a/12604120.xlsx
+++ b/12604120.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3FFE489-3858-46D0-9903-588DD7C04994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C61248-CC1C-4006-BFA1-4799324F5B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -292,6 +292,9 @@
   </si>
   <si>
     <t>Stressed</t>
+  </si>
+  <si>
+    <t>I had my Python CA today</t>
   </si>
 </sst>
 </file>
@@ -1951,7 +1954,9 @@
       <c r="B25" s="14">
         <v>420</v>
       </c>
-      <c r="C25" s="14"/>
+      <c r="C25" s="14">
+        <v>0</v>
+      </c>
       <c r="D25" s="14">
         <v>60</v>
       </c>
@@ -2133,7 +2138,9 @@
       <c r="B29" s="14">
         <v>360</v>
       </c>
-      <c r="C29" s="14"/>
+      <c r="C29" s="14">
+        <v>0</v>
+      </c>
       <c r="D29" s="14">
         <v>150</v>
       </c>
@@ -2177,7 +2184,9 @@
       <c r="B30" s="14">
         <v>360</v>
       </c>
-      <c r="C30" s="14"/>
+      <c r="C30" s="14">
+        <v>0</v>
+      </c>
       <c r="D30" s="14">
         <v>50</v>
       </c>
@@ -2215,26 +2224,50 @@
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B31" s="14">
+        <v>360</v>
+      </c>
+      <c r="C31" s="14">
+        <v>0</v>
+      </c>
+      <c r="D31" s="14">
+        <v>30</v>
+      </c>
+      <c r="E31" s="14">
+        <v>30</v>
+      </c>
+      <c r="F31" s="14">
+        <v>350</v>
+      </c>
+      <c r="G31" s="14">
+        <v>7</v>
+      </c>
+      <c r="H31" s="14">
+        <v>240</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>430</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="13"/>

--- a/12604120.xlsx
+++ b/12604120.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C61248-CC1C-4006-BFA1-4799324F5B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70B301E1-F1DA-450E-AC80-69CA8DACA6A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -295,6 +295,9 @@
   </si>
   <si>
     <t>I had my Python CA today</t>
+  </si>
+  <si>
+    <t>work on python project</t>
   </si>
 </sst>
 </file>
@@ -2270,26 +2273,50 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B32" s="14">
+        <v>360</v>
+      </c>
+      <c r="C32" s="14">
+        <v>0</v>
+      </c>
+      <c r="D32" s="14">
+        <v>30</v>
+      </c>
+      <c r="E32" s="14">
+        <v>0</v>
+      </c>
+      <c r="F32" s="14">
+        <v>350</v>
+      </c>
+      <c r="G32" s="14">
+        <v>7</v>
+      </c>
+      <c r="H32" s="14">
+        <v>300</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="13"/>
